--- a/data/reference/keti_experiment_lots.xlsx
+++ b/data/reference/keti_experiment_lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Dry electrode_홍지원\1. 과제 업무\2026년_Dry electrode\3. MLOps\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440794EA-63DC-4D87-B006-887098219613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910BD20D-205C-4062-9911-C381E1DB59BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1270,6 +1270,60 @@
     <xf numFmtId="10" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1279,31 +1333,19 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1315,49 +1357,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1974,638 +1974,638 @@
       <c r="BR1" s="4"/>
     </row>
     <row r="2" spans="2:87" x14ac:dyDescent="0.3">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="43" t="s">
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="44"/>
-      <c r="V2" s="44"/>
-      <c r="W2" s="45"/>
-      <c r="X2" s="43" t="s">
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="44"/>
-      <c r="AA2" s="44"/>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="44"/>
-      <c r="AD2" s="44"/>
-      <c r="AE2" s="44"/>
-      <c r="AF2" s="44"/>
-      <c r="AG2" s="44"/>
-      <c r="AH2" s="44"/>
-      <c r="AI2" s="44"/>
-      <c r="AJ2" s="44"/>
-      <c r="AK2" s="44"/>
-      <c r="AL2" s="44"/>
-      <c r="AM2" s="44"/>
-      <c r="AN2" s="44"/>
-      <c r="AO2" s="44"/>
-      <c r="AP2" s="44"/>
-      <c r="AQ2" s="44"/>
-      <c r="AR2" s="44"/>
-      <c r="AS2" s="44"/>
-      <c r="AT2" s="44"/>
-      <c r="AU2" s="44"/>
-      <c r="AV2" s="44"/>
-      <c r="AW2" s="44"/>
-      <c r="AX2" s="44"/>
-      <c r="AY2" s="44"/>
-      <c r="AZ2" s="44"/>
+      <c r="Y2" s="62"/>
+      <c r="Z2" s="62"/>
+      <c r="AA2" s="62"/>
+      <c r="AB2" s="62"/>
+      <c r="AC2" s="62"/>
+      <c r="AD2" s="62"/>
+      <c r="AE2" s="62"/>
+      <c r="AF2" s="62"/>
+      <c r="AG2" s="62"/>
+      <c r="AH2" s="62"/>
+      <c r="AI2" s="62"/>
+      <c r="AJ2" s="62"/>
+      <c r="AK2" s="62"/>
+      <c r="AL2" s="62"/>
+      <c r="AM2" s="62"/>
+      <c r="AN2" s="62"/>
+      <c r="AO2" s="62"/>
+      <c r="AP2" s="62"/>
+      <c r="AQ2" s="62"/>
+      <c r="AR2" s="62"/>
+      <c r="AS2" s="62"/>
+      <c r="AT2" s="62"/>
+      <c r="AU2" s="62"/>
+      <c r="AV2" s="62"/>
+      <c r="AW2" s="62"/>
+      <c r="AX2" s="62"/>
+      <c r="AY2" s="62"/>
+      <c r="AZ2" s="62"/>
       <c r="BA2" s="28"/>
       <c r="BB2" s="28"/>
       <c r="BC2" s="28"/>
       <c r="BD2" s="28"/>
       <c r="BE2" s="28"/>
-      <c r="BF2" s="43" t="s">
+      <c r="BF2" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="BG2" s="44"/>
-      <c r="BH2" s="44"/>
-      <c r="BI2" s="44"/>
-      <c r="BJ2" s="44"/>
-      <c r="BK2" s="44"/>
-      <c r="BL2" s="44"/>
-      <c r="BM2" s="44"/>
-      <c r="BN2" s="44"/>
-      <c r="BO2" s="45"/>
-      <c r="BP2" s="43" t="s">
+      <c r="BG2" s="62"/>
+      <c r="BH2" s="62"/>
+      <c r="BI2" s="62"/>
+      <c r="BJ2" s="62"/>
+      <c r="BK2" s="62"/>
+      <c r="BL2" s="62"/>
+      <c r="BM2" s="62"/>
+      <c r="BN2" s="62"/>
+      <c r="BO2" s="63"/>
+      <c r="BP2" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="BQ2" s="44"/>
-      <c r="BR2" s="44"/>
-      <c r="BS2" s="44"/>
-      <c r="BT2" s="44"/>
-      <c r="BU2" s="44"/>
-      <c r="BV2" s="44"/>
-      <c r="BW2" s="44"/>
-      <c r="BX2" s="44"/>
-      <c r="BY2" s="44"/>
-      <c r="BZ2" s="44"/>
-      <c r="CA2" s="44"/>
-      <c r="CB2" s="44"/>
-      <c r="CC2" s="44"/>
-      <c r="CD2" s="44"/>
-      <c r="CE2" s="45"/>
-      <c r="CF2" s="43" t="s">
+      <c r="BQ2" s="62"/>
+      <c r="BR2" s="62"/>
+      <c r="BS2" s="62"/>
+      <c r="BT2" s="62"/>
+      <c r="BU2" s="62"/>
+      <c r="BV2" s="62"/>
+      <c r="BW2" s="62"/>
+      <c r="BX2" s="62"/>
+      <c r="BY2" s="62"/>
+      <c r="BZ2" s="62"/>
+      <c r="CA2" s="62"/>
+      <c r="CB2" s="62"/>
+      <c r="CC2" s="62"/>
+      <c r="CD2" s="62"/>
+      <c r="CE2" s="63"/>
+      <c r="CF2" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="CG2" s="44"/>
-      <c r="CH2" s="44"/>
-      <c r="CI2" s="45"/>
+      <c r="CG2" s="62"/>
+      <c r="CH2" s="62"/>
+      <c r="CI2" s="63"/>
     </row>
     <row r="3" spans="2:87" x14ac:dyDescent="0.3">
-      <c r="B3" s="56"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="63" t="s">
+      <c r="B3" s="70"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63" t="s">
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="63"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63" t="s">
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64" t="s">
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="W3" s="64"/>
-      <c r="X3" s="43" t="s">
+      <c r="W3" s="65"/>
+      <c r="X3" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="Y3" s="44"/>
-      <c r="Z3" s="44"/>
-      <c r="AA3" s="44"/>
-      <c r="AB3" s="44"/>
-      <c r="AC3" s="44"/>
-      <c r="AD3" s="44"/>
-      <c r="AE3" s="44"/>
-      <c r="AF3" s="44"/>
-      <c r="AG3" s="44"/>
-      <c r="AH3" s="44"/>
-      <c r="AI3" s="44"/>
-      <c r="AJ3" s="44"/>
-      <c r="AK3" s="44"/>
-      <c r="AL3" s="44"/>
-      <c r="AM3" s="44"/>
-      <c r="AN3" s="44"/>
-      <c r="AO3" s="44"/>
-      <c r="AP3" s="44"/>
-      <c r="AQ3" s="44"/>
-      <c r="AR3" s="44"/>
-      <c r="AS3" s="44"/>
-      <c r="AT3" s="44"/>
-      <c r="AU3" s="45"/>
-      <c r="AV3" s="43" t="s">
+      <c r="Y3" s="62"/>
+      <c r="Z3" s="62"/>
+      <c r="AA3" s="62"/>
+      <c r="AB3" s="62"/>
+      <c r="AC3" s="62"/>
+      <c r="AD3" s="62"/>
+      <c r="AE3" s="62"/>
+      <c r="AF3" s="62"/>
+      <c r="AG3" s="62"/>
+      <c r="AH3" s="62"/>
+      <c r="AI3" s="62"/>
+      <c r="AJ3" s="62"/>
+      <c r="AK3" s="62"/>
+      <c r="AL3" s="62"/>
+      <c r="AM3" s="62"/>
+      <c r="AN3" s="62"/>
+      <c r="AO3" s="62"/>
+      <c r="AP3" s="62"/>
+      <c r="AQ3" s="62"/>
+      <c r="AR3" s="62"/>
+      <c r="AS3" s="62"/>
+      <c r="AT3" s="62"/>
+      <c r="AU3" s="63"/>
+      <c r="AV3" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="AW3" s="44"/>
-      <c r="AX3" s="44"/>
-      <c r="AY3" s="44"/>
-      <c r="AZ3" s="45"/>
-      <c r="BA3" s="43" t="s">
+      <c r="AW3" s="62"/>
+      <c r="AX3" s="62"/>
+      <c r="AY3" s="62"/>
+      <c r="AZ3" s="63"/>
+      <c r="BA3" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="BB3" s="44"/>
-      <c r="BC3" s="44"/>
-      <c r="BD3" s="44"/>
-      <c r="BE3" s="45"/>
-      <c r="BF3" s="43" t="s">
+      <c r="BB3" s="62"/>
+      <c r="BC3" s="62"/>
+      <c r="BD3" s="62"/>
+      <c r="BE3" s="63"/>
+      <c r="BF3" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="BG3" s="44"/>
-      <c r="BH3" s="44"/>
-      <c r="BI3" s="44"/>
-      <c r="BJ3" s="44"/>
-      <c r="BK3" s="44"/>
-      <c r="BL3" s="44"/>
-      <c r="BM3" s="44"/>
-      <c r="BN3" s="44"/>
-      <c r="BO3" s="45"/>
-      <c r="BP3" s="46" t="s">
+      <c r="BG3" s="62"/>
+      <c r="BH3" s="62"/>
+      <c r="BI3" s="62"/>
+      <c r="BJ3" s="62"/>
+      <c r="BK3" s="62"/>
+      <c r="BL3" s="62"/>
+      <c r="BM3" s="62"/>
+      <c r="BN3" s="62"/>
+      <c r="BO3" s="63"/>
+      <c r="BP3" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="BQ3" s="47"/>
-      <c r="BR3" s="47"/>
-      <c r="BS3" s="47"/>
-      <c r="BT3" s="47"/>
-      <c r="BU3" s="48"/>
-      <c r="BV3" s="43" t="s">
+      <c r="BQ3" s="59"/>
+      <c r="BR3" s="59"/>
+      <c r="BS3" s="59"/>
+      <c r="BT3" s="59"/>
+      <c r="BU3" s="60"/>
+      <c r="BV3" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="BW3" s="44"/>
-      <c r="BX3" s="44"/>
-      <c r="BY3" s="44"/>
-      <c r="BZ3" s="44"/>
-      <c r="CA3" s="44"/>
-      <c r="CB3" s="44"/>
-      <c r="CC3" s="44"/>
-      <c r="CD3" s="44"/>
-      <c r="CE3" s="45"/>
-      <c r="CF3" s="65" t="s">
+      <c r="BW3" s="62"/>
+      <c r="BX3" s="62"/>
+      <c r="BY3" s="62"/>
+      <c r="BZ3" s="62"/>
+      <c r="CA3" s="62"/>
+      <c r="CB3" s="62"/>
+      <c r="CC3" s="62"/>
+      <c r="CD3" s="62"/>
+      <c r="CE3" s="63"/>
+      <c r="CF3" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="CG3" s="58"/>
-      <c r="CH3" s="58"/>
-      <c r="CI3" s="66"/>
+      <c r="CG3" s="67"/>
+      <c r="CH3" s="67"/>
+      <c r="CI3" s="68"/>
     </row>
     <row r="4" spans="2:87" x14ac:dyDescent="0.3">
-      <c r="B4" s="56"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="46" t="s">
+      <c r="B4" s="70"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="Y4" s="47"/>
-      <c r="Z4" s="47"/>
-      <c r="AA4" s="47"/>
-      <c r="AB4" s="47"/>
-      <c r="AC4" s="48"/>
-      <c r="AD4" s="46" t="s">
+      <c r="Y4" s="59"/>
+      <c r="Z4" s="59"/>
+      <c r="AA4" s="59"/>
+      <c r="AB4" s="59"/>
+      <c r="AC4" s="60"/>
+      <c r="AD4" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="AE4" s="47"/>
-      <c r="AF4" s="47"/>
-      <c r="AG4" s="47"/>
-      <c r="AH4" s="47"/>
-      <c r="AI4" s="48"/>
-      <c r="AJ4" s="46" t="s">
+      <c r="AE4" s="59"/>
+      <c r="AF4" s="59"/>
+      <c r="AG4" s="59"/>
+      <c r="AH4" s="59"/>
+      <c r="AI4" s="60"/>
+      <c r="AJ4" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="AK4" s="47"/>
-      <c r="AL4" s="47"/>
-      <c r="AM4" s="47"/>
-      <c r="AN4" s="47"/>
-      <c r="AO4" s="48"/>
-      <c r="AP4" s="46" t="s">
+      <c r="AK4" s="59"/>
+      <c r="AL4" s="59"/>
+      <c r="AM4" s="59"/>
+      <c r="AN4" s="59"/>
+      <c r="AO4" s="60"/>
+      <c r="AP4" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="AQ4" s="47"/>
-      <c r="AR4" s="47"/>
-      <c r="AS4" s="47"/>
-      <c r="AT4" s="47"/>
-      <c r="AU4" s="48"/>
-      <c r="AV4" s="46" t="s">
+      <c r="AQ4" s="59"/>
+      <c r="AR4" s="59"/>
+      <c r="AS4" s="59"/>
+      <c r="AT4" s="59"/>
+      <c r="AU4" s="60"/>
+      <c r="AV4" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="AW4" s="47"/>
-      <c r="AX4" s="47"/>
-      <c r="AY4" s="47"/>
-      <c r="AZ4" s="48"/>
-      <c r="BA4" s="46" t="s">
+      <c r="AW4" s="59"/>
+      <c r="AX4" s="59"/>
+      <c r="AY4" s="59"/>
+      <c r="AZ4" s="60"/>
+      <c r="BA4" s="58" t="s">
         <v>80</v>
       </c>
-      <c r="BB4" s="47"/>
-      <c r="BC4" s="47"/>
-      <c r="BD4" s="47"/>
-      <c r="BE4" s="48"/>
-      <c r="BF4" s="46" t="s">
+      <c r="BB4" s="59"/>
+      <c r="BC4" s="59"/>
+      <c r="BD4" s="59"/>
+      <c r="BE4" s="60"/>
+      <c r="BF4" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="BG4" s="47"/>
-      <c r="BH4" s="47"/>
-      <c r="BI4" s="47"/>
-      <c r="BJ4" s="48"/>
-      <c r="BK4" s="46" t="s">
+      <c r="BG4" s="59"/>
+      <c r="BH4" s="59"/>
+      <c r="BI4" s="59"/>
+      <c r="BJ4" s="60"/>
+      <c r="BK4" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="BL4" s="47"/>
-      <c r="BM4" s="47"/>
-      <c r="BN4" s="47"/>
-      <c r="BO4" s="48"/>
-      <c r="BP4" s="43" t="s">
+      <c r="BL4" s="59"/>
+      <c r="BM4" s="59"/>
+      <c r="BN4" s="59"/>
+      <c r="BO4" s="60"/>
+      <c r="BP4" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="BQ4" s="44"/>
-      <c r="BR4" s="44"/>
-      <c r="BS4" s="44"/>
-      <c r="BT4" s="44"/>
-      <c r="BU4" s="45"/>
-      <c r="BV4" s="43" t="s">
+      <c r="BQ4" s="62"/>
+      <c r="BR4" s="62"/>
+      <c r="BS4" s="62"/>
+      <c r="BT4" s="62"/>
+      <c r="BU4" s="63"/>
+      <c r="BV4" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="BW4" s="44"/>
-      <c r="BX4" s="44"/>
-      <c r="BY4" s="44"/>
-      <c r="BZ4" s="44"/>
-      <c r="CA4" s="44"/>
-      <c r="CB4" s="44"/>
-      <c r="CC4" s="44"/>
-      <c r="CD4" s="44"/>
-      <c r="CE4" s="45"/>
-      <c r="CF4" s="46"/>
-      <c r="CG4" s="47"/>
-      <c r="CH4" s="47"/>
-      <c r="CI4" s="48"/>
+      <c r="BW4" s="62"/>
+      <c r="BX4" s="62"/>
+      <c r="BY4" s="62"/>
+      <c r="BZ4" s="62"/>
+      <c r="CA4" s="62"/>
+      <c r="CB4" s="62"/>
+      <c r="CC4" s="62"/>
+      <c r="CD4" s="62"/>
+      <c r="CE4" s="63"/>
+      <c r="CF4" s="58"/>
+      <c r="CG4" s="59"/>
+      <c r="CH4" s="59"/>
+      <c r="CI4" s="60"/>
     </row>
     <row r="5" spans="2:87" x14ac:dyDescent="0.3">
-      <c r="B5" s="56"/>
-      <c r="C5" s="61" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="61" t="s">
+      <c r="D5" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="62" t="s">
+      <c r="E5" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="60" t="s">
+      <c r="F5" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="61" t="s">
+      <c r="G5" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="61" t="s">
+      <c r="H5" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="61" t="s">
+      <c r="I5" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62" t="s">
+      <c r="J5" s="52"/>
+      <c r="K5" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="60" t="s">
+      <c r="L5" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="M5" s="61" t="s">
+      <c r="M5" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="N5" s="61" t="s">
+      <c r="N5" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="O5" s="62" t="s">
+      <c r="O5" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="P5" s="60" t="s">
+      <c r="P5" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="Q5" s="61" t="s">
+      <c r="Q5" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="R5" s="61" t="s">
+      <c r="R5" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="S5" s="61" t="s">
+      <c r="S5" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="T5" s="61"/>
-      <c r="U5" s="62" t="s">
+      <c r="T5" s="52"/>
+      <c r="U5" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="V5" s="49" t="s">
+      <c r="V5" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="W5" s="53" t="s">
+      <c r="W5" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="X5" s="49" t="s">
+      <c r="X5" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="Y5" s="51"/>
-      <c r="Z5" s="51" t="s">
+      <c r="Y5" s="50"/>
+      <c r="Z5" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="AA5" s="51" t="s">
+      <c r="AA5" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="AB5" s="51" t="s">
+      <c r="AB5" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="AC5" s="53" t="s">
+      <c r="AC5" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="AD5" s="49" t="s">
+      <c r="AD5" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="AE5" s="51"/>
-      <c r="AF5" s="51" t="s">
+      <c r="AE5" s="50"/>
+      <c r="AF5" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="AG5" s="51" t="s">
+      <c r="AG5" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="AH5" s="51" t="s">
+      <c r="AH5" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="AI5" s="53" t="s">
+      <c r="AI5" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="AJ5" s="49" t="s">
+      <c r="AJ5" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="AK5" s="51"/>
-      <c r="AL5" s="51" t="s">
+      <c r="AK5" s="50"/>
+      <c r="AL5" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="AM5" s="51" t="s">
+      <c r="AM5" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="AN5" s="51" t="s">
+      <c r="AN5" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="AO5" s="53" t="s">
+      <c r="AO5" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="AP5" s="49" t="s">
+      <c r="AP5" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="AQ5" s="51"/>
-      <c r="AR5" s="51" t="s">
+      <c r="AQ5" s="50"/>
+      <c r="AR5" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="AS5" s="51" t="s">
+      <c r="AS5" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="AT5" s="51" t="s">
+      <c r="AT5" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="AU5" s="53" t="s">
+      <c r="AU5" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="AV5" s="49" t="s">
+      <c r="AV5" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="AW5" s="51" t="s">
+      <c r="AW5" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="AX5" s="51" t="s">
+      <c r="AX5" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="AY5" s="51" t="s">
+      <c r="AY5" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="AZ5" s="53" t="s">
+      <c r="AZ5" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="BA5" s="49" t="s">
+      <c r="BA5" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="BB5" s="51" t="s">
+      <c r="BB5" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="BC5" s="51" t="s">
+      <c r="BC5" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="BD5" s="51" t="s">
+      <c r="BD5" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="BE5" s="53" t="s">
+      <c r="BE5" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="BF5" s="49" t="s">
+      <c r="BF5" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="BG5" s="51" t="s">
+      <c r="BG5" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="BH5" s="51" t="s">
+      <c r="BH5" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="BI5" s="51" t="s">
+      <c r="BI5" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="BJ5" s="53" t="s">
+      <c r="BJ5" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="BK5" s="49" t="s">
+      <c r="BK5" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="BL5" s="51" t="s">
+      <c r="BL5" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="BM5" s="51" t="s">
+      <c r="BM5" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="BN5" s="51" t="s">
+      <c r="BN5" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="BO5" s="53" t="s">
+      <c r="BO5" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="BP5" s="49" t="s">
+      <c r="BP5" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="BQ5" s="51"/>
-      <c r="BR5" s="53"/>
-      <c r="BS5" s="51" t="s">
+      <c r="BQ5" s="50"/>
+      <c r="BR5" s="43"/>
+      <c r="BS5" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="BT5" s="51"/>
-      <c r="BU5" s="53"/>
-      <c r="BV5" s="60" t="s">
+      <c r="BT5" s="50"/>
+      <c r="BU5" s="43"/>
+      <c r="BV5" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="BW5" s="61"/>
-      <c r="BX5" s="61"/>
-      <c r="BY5" s="62"/>
-      <c r="BZ5" s="49" t="s">
+      <c r="BW5" s="52"/>
+      <c r="BX5" s="52"/>
+      <c r="BY5" s="53"/>
+      <c r="BZ5" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="CA5" s="51"/>
-      <c r="CB5" s="51"/>
-      <c r="CC5" s="53"/>
-      <c r="CD5" s="71" t="s">
+      <c r="CA5" s="50"/>
+      <c r="CB5" s="50"/>
+      <c r="CC5" s="43"/>
+      <c r="CD5" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="CE5" s="72"/>
-      <c r="CF5" s="67" t="s">
+      <c r="CE5" s="55"/>
+      <c r="CF5" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="CG5" s="67" t="s">
+      <c r="CG5" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="CH5" s="49" t="s">
+      <c r="CH5" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="CI5" s="53"/>
+      <c r="CI5" s="43"/>
     </row>
     <row r="6" spans="2:87" x14ac:dyDescent="0.3">
-      <c r="B6" s="56"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
+      <c r="B6" s="70"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
       <c r="I6" s="7" t="s">
         <v>55</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="K6" s="54"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="52"/>
-      <c r="R6" s="52"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="57"/>
+      <c r="R6" s="57"/>
       <c r="S6" s="7" t="s">
         <v>55</v>
       </c>
       <c r="T6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="U6" s="54"/>
-      <c r="V6" s="50"/>
-      <c r="W6" s="54"/>
+      <c r="U6" s="44"/>
+      <c r="V6" s="56"/>
+      <c r="W6" s="44"/>
       <c r="X6" s="8" t="s">
         <v>57</v>
       </c>
       <c r="Y6" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="Z6" s="52"/>
-      <c r="AA6" s="52"/>
-      <c r="AB6" s="52"/>
-      <c r="AC6" s="54"/>
+      <c r="Z6" s="57"/>
+      <c r="AA6" s="57"/>
+      <c r="AB6" s="57"/>
+      <c r="AC6" s="44"/>
       <c r="AD6" s="8" t="s">
         <v>57</v>
       </c>
       <c r="AE6" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="AF6" s="52"/>
-      <c r="AG6" s="52"/>
-      <c r="AH6" s="52"/>
-      <c r="AI6" s="54"/>
+      <c r="AF6" s="57"/>
+      <c r="AG6" s="57"/>
+      <c r="AH6" s="57"/>
+      <c r="AI6" s="44"/>
       <c r="AJ6" s="8" t="s">
         <v>57</v>
       </c>
       <c r="AK6" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="AL6" s="52"/>
-      <c r="AM6" s="52"/>
-      <c r="AN6" s="52"/>
-      <c r="AO6" s="54"/>
+      <c r="AL6" s="57"/>
+      <c r="AM6" s="57"/>
+      <c r="AN6" s="57"/>
+      <c r="AO6" s="44"/>
       <c r="AP6" s="8" t="s">
         <v>57</v>
       </c>
       <c r="AQ6" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="AR6" s="52"/>
-      <c r="AS6" s="52"/>
-      <c r="AT6" s="52"/>
-      <c r="AU6" s="54"/>
-      <c r="AV6" s="50"/>
-      <c r="AW6" s="52"/>
-      <c r="AX6" s="52"/>
-      <c r="AY6" s="52"/>
-      <c r="AZ6" s="54"/>
-      <c r="BA6" s="50"/>
-      <c r="BB6" s="52"/>
-      <c r="BC6" s="52"/>
-      <c r="BD6" s="52"/>
-      <c r="BE6" s="54"/>
-      <c r="BF6" s="50"/>
-      <c r="BG6" s="52"/>
-      <c r="BH6" s="52"/>
-      <c r="BI6" s="52"/>
-      <c r="BJ6" s="54"/>
-      <c r="BK6" s="50"/>
-      <c r="BL6" s="52"/>
-      <c r="BM6" s="52"/>
-      <c r="BN6" s="52"/>
-      <c r="BO6" s="54"/>
+      <c r="AR6" s="57"/>
+      <c r="AS6" s="57"/>
+      <c r="AT6" s="57"/>
+      <c r="AU6" s="44"/>
+      <c r="AV6" s="56"/>
+      <c r="AW6" s="57"/>
+      <c r="AX6" s="57"/>
+      <c r="AY6" s="57"/>
+      <c r="AZ6" s="44"/>
+      <c r="BA6" s="56"/>
+      <c r="BB6" s="57"/>
+      <c r="BC6" s="57"/>
+      <c r="BD6" s="57"/>
+      <c r="BE6" s="44"/>
+      <c r="BF6" s="56"/>
+      <c r="BG6" s="57"/>
+      <c r="BH6" s="57"/>
+      <c r="BI6" s="57"/>
+      <c r="BJ6" s="44"/>
+      <c r="BK6" s="56"/>
+      <c r="BL6" s="57"/>
+      <c r="BM6" s="57"/>
+      <c r="BN6" s="57"/>
+      <c r="BO6" s="44"/>
       <c r="BP6" s="8" t="s">
         <v>59</v>
       </c>
@@ -2648,12 +2648,12 @@
       <c r="CC6" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="CD6" s="69">
+      <c r="CD6" s="48">
         <v>0.8</v>
       </c>
-      <c r="CE6" s="70"/>
-      <c r="CF6" s="68"/>
-      <c r="CG6" s="68"/>
+      <c r="CE6" s="49"/>
+      <c r="CF6" s="46"/>
+      <c r="CG6" s="46"/>
       <c r="CH6" s="8" t="s">
         <v>45</v>
       </c>
@@ -2662,7 +2662,7 @@
       </c>
     </row>
     <row r="7" spans="2:87" x14ac:dyDescent="0.3">
-      <c r="B7" s="57"/>
+      <c r="B7" s="71"/>
       <c r="C7" s="10" t="s">
         <v>62</v>
       </c>
@@ -4346,10 +4346,18 @@
       </c>
       <c r="CD13" s="25"/>
       <c r="CE13" s="42"/>
-      <c r="CF13" s="20"/>
-      <c r="CG13" s="20"/>
-      <c r="CH13" s="25"/>
-      <c r="CI13" s="27"/>
+      <c r="CF13" s="20">
+        <v>0.6</v>
+      </c>
+      <c r="CG13" s="20">
+        <v>20.13</v>
+      </c>
+      <c r="CH13" s="1">
+        <v>5</v>
+      </c>
+      <c r="CI13" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="2:87" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="17" t="s">
@@ -4586,10 +4594,18 @@
       <c r="CE14" s="42">
         <v>0.80100000000000005</v>
       </c>
-      <c r="CF14" s="20"/>
-      <c r="CG14" s="20"/>
-      <c r="CH14" s="25"/>
-      <c r="CI14" s="27"/>
+      <c r="CF14" s="20">
+        <v>11.8</v>
+      </c>
+      <c r="CG14" s="20">
+        <v>1.2871999999999999</v>
+      </c>
+      <c r="CH14" s="1">
+        <v>5</v>
+      </c>
+      <c r="CI14" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="2:87" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="17" t="s">
@@ -5304,47 +5320,45 @@
     </row>
   </sheetData>
   <mergeCells count="96">
-    <mergeCell ref="BO5:BO6"/>
-    <mergeCell ref="CG5:CG6"/>
-    <mergeCell ref="CH5:CI5"/>
-    <mergeCell ref="CD6:CE6"/>
-    <mergeCell ref="BP5:BR5"/>
-    <mergeCell ref="BS5:BU5"/>
-    <mergeCell ref="BV5:BY5"/>
-    <mergeCell ref="BZ5:CC5"/>
-    <mergeCell ref="CD5:CE5"/>
-    <mergeCell ref="CF5:CF6"/>
-    <mergeCell ref="BJ5:BJ6"/>
-    <mergeCell ref="BK5:BK6"/>
-    <mergeCell ref="BL5:BL6"/>
-    <mergeCell ref="BM5:BM6"/>
-    <mergeCell ref="BN5:BN6"/>
-    <mergeCell ref="BI5:BI6"/>
-    <mergeCell ref="AS5:AS6"/>
-    <mergeCell ref="AT5:AT6"/>
-    <mergeCell ref="AU5:AU6"/>
-    <mergeCell ref="AV5:AV6"/>
-    <mergeCell ref="AW5:AW6"/>
-    <mergeCell ref="AX5:AX6"/>
-    <mergeCell ref="AY5:AY6"/>
-    <mergeCell ref="AZ5:AZ6"/>
-    <mergeCell ref="BF5:BF6"/>
-    <mergeCell ref="BG5:BG6"/>
-    <mergeCell ref="BH5:BH6"/>
-    <mergeCell ref="AA5:AA6"/>
-    <mergeCell ref="AB5:AB6"/>
-    <mergeCell ref="AR5:AR6"/>
-    <mergeCell ref="AD5:AE5"/>
-    <mergeCell ref="AF5:AF6"/>
-    <mergeCell ref="AG5:AG6"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="AJ5:AK5"/>
-    <mergeCell ref="AL5:AL6"/>
-    <mergeCell ref="AM5:AM6"/>
-    <mergeCell ref="AN5:AN6"/>
-    <mergeCell ref="AO5:AO6"/>
-    <mergeCell ref="AP5:AQ5"/>
+    <mergeCell ref="BA3:BE3"/>
+    <mergeCell ref="BA4:BE4"/>
+    <mergeCell ref="BA5:BA6"/>
+    <mergeCell ref="BB5:BB6"/>
+    <mergeCell ref="BC5:BC6"/>
+    <mergeCell ref="BD5:BD6"/>
+    <mergeCell ref="BE5:BE6"/>
+    <mergeCell ref="B2:B7"/>
+    <mergeCell ref="C2:E4"/>
+    <mergeCell ref="F2:W2"/>
+    <mergeCell ref="X2:AZ2"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="AP4:AU4"/>
+    <mergeCell ref="AV4:AZ4"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="BF2:BO2"/>
+    <mergeCell ref="BP2:CE2"/>
+    <mergeCell ref="CF2:CI2"/>
+    <mergeCell ref="F3:K4"/>
+    <mergeCell ref="L3:O4"/>
+    <mergeCell ref="P3:U4"/>
+    <mergeCell ref="V3:W4"/>
+    <mergeCell ref="X3:AU3"/>
+    <mergeCell ref="AV3:AZ3"/>
+    <mergeCell ref="BF3:BO3"/>
+    <mergeCell ref="BP3:BU3"/>
+    <mergeCell ref="BV3:CE3"/>
+    <mergeCell ref="CF3:CI4"/>
+    <mergeCell ref="X4:AC4"/>
+    <mergeCell ref="AD4:AI4"/>
+    <mergeCell ref="AJ4:AO4"/>
     <mergeCell ref="BF4:BJ4"/>
     <mergeCell ref="BK4:BO4"/>
     <mergeCell ref="BP4:BU4"/>
@@ -5361,45 +5375,47 @@
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="Q5:Q6"/>
     <mergeCell ref="R5:R6"/>
-    <mergeCell ref="BF2:BO2"/>
-    <mergeCell ref="BP2:CE2"/>
-    <mergeCell ref="CF2:CI2"/>
-    <mergeCell ref="F3:K4"/>
-    <mergeCell ref="L3:O4"/>
-    <mergeCell ref="P3:U4"/>
-    <mergeCell ref="V3:W4"/>
-    <mergeCell ref="X3:AU3"/>
-    <mergeCell ref="AV3:AZ3"/>
-    <mergeCell ref="BF3:BO3"/>
-    <mergeCell ref="BP3:BU3"/>
-    <mergeCell ref="BV3:CE3"/>
-    <mergeCell ref="CF3:CI4"/>
-    <mergeCell ref="X4:AC4"/>
-    <mergeCell ref="AD4:AI4"/>
-    <mergeCell ref="AJ4:AO4"/>
-    <mergeCell ref="B2:B7"/>
-    <mergeCell ref="C2:E4"/>
-    <mergeCell ref="F2:W2"/>
-    <mergeCell ref="X2:AZ2"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="AP4:AU4"/>
-    <mergeCell ref="AV4:AZ4"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="W5:W6"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="Z5:Z6"/>
-    <mergeCell ref="BA3:BE3"/>
-    <mergeCell ref="BA4:BE4"/>
-    <mergeCell ref="BA5:BA6"/>
-    <mergeCell ref="BB5:BB6"/>
-    <mergeCell ref="BC5:BC6"/>
-    <mergeCell ref="BD5:BD6"/>
-    <mergeCell ref="BE5:BE6"/>
+    <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="AR5:AR6"/>
+    <mergeCell ref="AD5:AE5"/>
+    <mergeCell ref="AF5:AF6"/>
+    <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="AH5:AH6"/>
+    <mergeCell ref="AI5:AI6"/>
+    <mergeCell ref="AJ5:AK5"/>
+    <mergeCell ref="AL5:AL6"/>
+    <mergeCell ref="AM5:AM6"/>
+    <mergeCell ref="AN5:AN6"/>
+    <mergeCell ref="AO5:AO6"/>
+    <mergeCell ref="AP5:AQ5"/>
+    <mergeCell ref="BI5:BI6"/>
+    <mergeCell ref="AS5:AS6"/>
+    <mergeCell ref="AT5:AT6"/>
+    <mergeCell ref="AU5:AU6"/>
+    <mergeCell ref="AV5:AV6"/>
+    <mergeCell ref="AW5:AW6"/>
+    <mergeCell ref="AX5:AX6"/>
+    <mergeCell ref="AY5:AY6"/>
+    <mergeCell ref="AZ5:AZ6"/>
+    <mergeCell ref="BF5:BF6"/>
+    <mergeCell ref="BG5:BG6"/>
+    <mergeCell ref="BH5:BH6"/>
+    <mergeCell ref="BJ5:BJ6"/>
+    <mergeCell ref="BK5:BK6"/>
+    <mergeCell ref="BL5:BL6"/>
+    <mergeCell ref="BM5:BM6"/>
+    <mergeCell ref="BN5:BN6"/>
+    <mergeCell ref="BO5:BO6"/>
+    <mergeCell ref="CG5:CG6"/>
+    <mergeCell ref="CH5:CI5"/>
+    <mergeCell ref="CD6:CE6"/>
+    <mergeCell ref="BP5:BR5"/>
+    <mergeCell ref="BS5:BU5"/>
+    <mergeCell ref="BV5:BY5"/>
+    <mergeCell ref="BZ5:CC5"/>
+    <mergeCell ref="CD5:CE5"/>
+    <mergeCell ref="CF5:CF6"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
